--- a/etf_holdings/2026-10-30_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.47%6405</t>
+          <t>-1.41%6315</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6405</v>
+        <v>6315</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.69%260,000</t>
+          <t>7.89%260,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>7.89%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-3.85%1250</t>
+          <t>-4.8%1190</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1250</v>
+        <v>1190</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.50%1,299,000</t>
+          <t>7.43%1,299,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.50%</t>
+          <t>7.43%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.45%1040</t>
+          <t>-4.9%989</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1040</v>
+        <v>989</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.35%1,530,000</t>
+          <t>7.28%1,530,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.35%</t>
+          <t>7.28%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-5.38%4840</t>
+          <t>-4.75%4610</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.38%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4840</v>
+        <v>4610</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.22%323,000</t>
+          <t>7.16%323,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.22%</t>
+          <t>7.16%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.82%16980</t>
+          <t>-5.95%15970</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-5.95%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>16980</v>
+        <v>15970</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.16%91,300</t>
+          <t>7.01%91,300</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.16%</t>
+          <t>7.01%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-5.91%1115</t>
+          <t>-3.21%3915</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1115</v>
+        <v>3915</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.81%1,127,000</t>
+          <t>5.53%294,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.81%</t>
+          <t>5.53%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1127000</v>
+        <v>294000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.49%4045</t>
+          <t>-8.52%1020</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.49%</t>
+          <t>-8.52%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4045</v>
+        <v>1020</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.50%294,000</t>
+          <t>5.53%1,127,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>5.53%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>294000</v>
+        <v>1127000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-5.8%1705</t>
+          <t>-4.69%1625</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1705</v>
+        <v>1625</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.24%665,000</t>
+          <t>5.20%665,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>5.20%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.31%1755</t>
+          <t>-6.69%4675</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>-6.69%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1755</v>
+        <v>4675</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.94%609,000</t>
+          <t>4.77%212,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.94%</t>
+          <t>4.77%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>609000</v>
+        <v>212000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.3%5010</t>
+          <t>-7.98%1615</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-7.98%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5010</v>
+        <v>1615</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.91%212,000</t>
+          <t>4.73%609,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.73%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>212000</v>
+        <v>609000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.24%841</t>
+          <t>-7.73%776</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-7.73%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>841</v>
+        <v>776</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.00%1,030,000</t>
+          <t>3.84%1,030,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>3.84%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.42%2425</t>
+          <t>-1.65%2385</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.42%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2425</v>
+        <v>2385</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.04%271,000</t>
+          <t>3.11%271,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-6.74%5190</t>
+          <t>-4.62%4950</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.74%</t>
+          <t>-4.62%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5190</v>
+        <v>4950</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.88%120,000</t>
+          <t>2.86%120,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-6.49%7640</t>
+          <t>-0.07%7635</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.49%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7640</v>
+        <v>7635</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.58%73,000</t>
+          <t>2.68%73,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:44</t>
+          <t>2026-10-30 23:08:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.66%9880</t>
+          <t>-2.33%9650</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.66%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9880</v>
+        <v>9650</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.28%50,000</t>
+          <t>2.32%50,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.41%2415</t>
+          <t>-1.86%2370</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2415</v>
+        <v>2370</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.00%179,000</t>
+          <t>2.04%179,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.09%1390</t>
+          <t>-0.32%3095</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1390</v>
+        <v>3095</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.97%306,000</t>
+          <t>1.90%128,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>306000</v>
+        <v>128000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.42%3105</t>
+          <t>-8.99%1265</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.42%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3105</v>
+        <v>1265</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.84%128,000</t>
+          <t>1.86%306,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>128000</v>
+        <v>306000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.52%1545</t>
+          <t>-7.12%1435</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-7.12%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1545</v>
+        <v>1435</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.43%200,000</t>
+          <t>1.38%200,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-3.33%1885</t>
+          <t>-3.98%1810</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1885</v>
+        <v>1810</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-6.32%1260</t>
+          <t>-5.56%1190</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.32%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1260</v>
+        <v>1190</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.86%148,000</t>
+          <t>0.85%148,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,34 +1785,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6415矽力*-KY</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-4.52%1480</t>
+          <t>-4.2%502</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.52%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1480</v>
+        <v>502</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.64%94,000</t>
+          <t>0.60%250,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>94000</v>
+        <v>250000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6415矽力*-KY</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.19%524</t>
+          <t>-9.8%1335</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>524</v>
+        <v>1335</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.61%250,000</t>
+          <t>0.60%94,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>250000</v>
+        <v>94000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-5.67%4655</t>
+          <t>-1.93%4565</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.67%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4655</v>
+        <v>4565</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.49%23,000</t>
+          <t>0.50%23,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-7.34%959</t>
+          <t>-2.82%932</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-7.34%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>959</v>
+        <v>932</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-6.57%156.5</t>
+          <t>-7.99%144</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-6.57%</t>
+          <t>-7.99%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>156.5</v>
+        <v>144</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-3.81%227.5</t>
+          <t>-6.37%213</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.81%</t>
+          <t>-6.37%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>227.5</v>
+        <v>213</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.11%100,000</t>
+          <t>0.10%100,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.88%269.5</t>
+          <t>-5.94%253.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-5.94%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>269.5</v>
+        <v>253.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.42%236.5</t>
+          <t>-6.77%220.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-6.77%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>236.5</v>
+        <v>220.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:46</t>
+          <t>2026-10-30 23:08:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-8.21%5815</t>
+          <t>-6.62%5430</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-8.21%</t>
+          <t>-6.62%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5815</v>
+        <v>5430</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-2.5%428.5</t>
+          <t>-2.33%418.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>428.5</v>
+        <v>418.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.16%3680</t>
+          <t>-6.93%3425</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>-6.93%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3680</v>
+        <v>3425</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.32%673</t>
+          <t>+1.04%680</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.32%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-9.77%115.5</t>
+          <t>-3.46%111.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-9.77%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>115.5</v>
+        <v>111.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-10%2880</t>
+          <t>-2.08%2820</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2.08%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2880</v>
+        <v>2820</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.68%275</t>
+          <t>-8.18%252.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>-8.18%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>275</v>
+        <v>252.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+3.33%1240</t>
+          <t>-4.03%1190</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>-4.03%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1240</v>
+        <v>1190</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.93%433</t>
+          <t>-5.54%409</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>-5.54%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.01%5,000</t>
+          <t>&lt;0.01%5,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.73%683</t>
+          <t>-2.2%668</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.81%1900</t>
+          <t>-2.11%1860</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.81%</t>
+          <t>-2.11%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1900</v>
+        <v>1860</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-3.5%165.5</t>
+          <t>-2.42%161.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>165.5</v>
+        <v>161.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-2.19%312</t>
+          <t>-5.13%296</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-5.13%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-3.73%1290</t>
+          <t>-2.71%1255</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.73%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1290</v>
+        <v>1255</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.88%1150</t>
+          <t>-6.52%1075</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-6.52%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1150</v>
+        <v>1075</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:47</t>
+          <t>2026-10-30 23:09:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-3.28%97.2</t>
+          <t>-6.48%90.9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-6.48%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>97.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-30_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:57</t>
+          <t>2026-10-30 23:20:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:59</t>
+          <t>2026-10-30 23:20:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:00</t>
+          <t>2026-10-30 23:20:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-30_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:40</t>
+          <t>2026-10-30 23:56:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:41</t>
+          <t>2026-10-30 23:56:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:42</t>
+          <t>2026-10-30 23:56:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
